--- a/out/Attention-S4_repeat_2_000006.xlsx
+++ b/out/Attention-S4_repeat_2_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>2.648249220197787</v>
+        <v>2.499999930000002</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.648249220197787</v>
+        <v>2.499999930000002</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>3.248249220197787</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>3.248249220197787</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>3.248249220197787</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>3.248249220197787</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3648012947504813</v>
+        <v>-0.3999999825000004</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>3.248249220197787</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>3.248249220197787</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>3.248249220197787</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>3.248249220197787</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>3.248249220197787</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>3.248249220197787</v>
+        <v>2.499999930000002</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.648249220197787</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.3999999825000004</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3648012947504813</v>
+        <v>-0.3999999825000004</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>3.248249220197787</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>3.248249220197787</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>3.248249220197787</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3648012947504813</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3648012947504813</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9648012947504814</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9648012947504814</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9648012947504814</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.648249220197787</v>
+        <v>-0.3999999825000004</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>3.248249220197787</v>
+        <v>2.499999930000002</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3648012947504813</v>
+        <v>2.499999930000002</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3648012947504813</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.9648012947504814</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.9648012947504814</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.9648012947504814</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.9648012947504814</v>
+        <v>2.499999930000002</v>
       </c>
       <c r="JC48" t="n">
-        <v>-1.869338789233006e-05</v>
+        <v>-0.0003106823225681437</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0574299681421693</v>
+        <v>0.9544832859844768</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9648012947504814</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.1149559245705088</v>
+        <v>1.910556488958182</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01098863939975576</v>
+        <v>0.1826296219860515</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.3999999825000004</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.07941910241671558</v>
+        <v>1.319939565385544</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01924764405023872</v>
+        <v>0.3198928856163341</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.3999999825000004</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.1069311376639663</v>
+        <v>1.777185673747872</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.01053957933579559</v>
+        <v>0.1751849852561705</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.1087471929584714</v>
+        <v>1.807387071817878</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.004350125898167171</v>
+        <v>0.07235414699142312</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.1068990254588795</v>
+        <v>1.776726255047776</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.005420851300212872</v>
+        <v>0.0901470581367613</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.1133911867290754</v>
+        <v>1.884678368649492</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.003262045427652021</v>
+        <v>0.05428017350714798</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.1144914816815832</v>
+        <v>1.903030483807713</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.002477911654897917</v>
+        <v>0.04126752390961348</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.1161859408406725</v>
+        <v>1.931262163537627</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.001093200817303421</v>
+        <v>0.01825193882915474</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.1158924719073689</v>
+        <v>1.926463710152257</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.0008676852873857978</v>
+        <v>0.01448258465532955</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.1165327356065775</v>
+        <v>1.937171767569312</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.0004277560855517731</v>
+        <v>0.007179251316212095</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>3.248249220197787</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.1165200119845022</v>
+        <v>1.937038525757359</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0002451912641241405</v>
+        <v>0.004172612270724021</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3648012947504813</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.1165853208673967</v>
+        <v>1.938201112639739</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0001200956320620703</v>
+        <v>0.00208380613536201</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3648012947504813</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1165801651148903</v>
+        <v>1.938193511935095</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.824225957239745e-05</v>
+        <v>0.001026998690295031</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>3.248249220197787</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.1165735642006141</v>
+        <v>1.938162353330768</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>3.17141805569301e-05</v>
+        <v>0.0005957775000224925</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>3.248249220197787</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.1165787170341371</v>
+        <v>1.938323490606596</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>6.159850569859539e-06</v>
+        <v>0.0001958773102574717</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3648012947504813</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.1165615258697967</v>
+        <v>1.93811897584786</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.73737344181313e-06</v>
+        <v>9.606060162719694e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3648012947504813</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.1165566004203176</v>
+        <v>1.938115094105672</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>-2.553803869891494e-06</v>
+        <v>4.881631486238714e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.1165521992917126</v>
+        <v>1.938119055715449</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>-2.629819553036738e-06</v>
+        <v>2.107198491659588e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.1165470441031398</v>
+        <v>1.938112272534135</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0</v>
+        <v>1.245520447377725e-05</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.11654758377104</v>
+        <v>1.938113726816028</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0</v>
+        <v>2.732487839350877e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.1165472516677168</v>
+        <v>1.938106724525208</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.1165476322027745</v>
+        <v>1.938102862450112</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0</v>
+        <v>-1.814378588387752e-06</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.1165478605238092</v>
+        <v>1.938098315137927</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.1165479504684592</v>
+        <v>1.938098405082576</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.1165470925348743</v>
+        <v>1.938097547148991</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>3.248249220197787</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.116547320855909</v>
+        <v>1.938097775470026</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3648012947504813</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.1165465251916973</v>
+        <v>1.938096979805815</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3648012947504813</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.1165465874610704</v>
+        <v>1.938097042075188</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>3.248249220197787</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.1165466151363472</v>
+        <v>1.938097069750464</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3648012947504813</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.1165467673503705</v>
+        <v>1.938097221964487</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3648012947504813</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.1165464214094088</v>
+        <v>1.938096876023526</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.1165464975164204</v>
+        <v>1.938096952130538</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.116546663568082</v>
+        <v>1.938097118182199</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.1165470233466821</v>
+        <v>1.938097477960799</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.1165470441031398</v>
+        <v>1.938097498717257</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.1165471478854283</v>
+        <v>1.938097602499545</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.116547376206463</v>
+        <v>1.93809783082058</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.1165472516677168</v>
+        <v>1.938097706281834</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.1165472793429936</v>
+        <v>1.938097733957111</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.1165473346935476</v>
+        <v>1.938097789307665</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.1165475976086783</v>
+        <v>1.938098052222795</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.1165475145828475</v>
+        <v>1.938097969196964</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.1165473070182707</v>
+        <v>1.938097761632388</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.116547320855909</v>
+        <v>1.938097775470026</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.1165474592322938</v>
+        <v>1.938097913846411</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.1165471755607051</v>
+        <v>1.938097630174822</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.1165470025902244</v>
+        <v>1.938097457204341</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.1165468988079359</v>
+        <v>1.938097353422053</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.1165470441031398</v>
+        <v>1.938097498717257</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.116547286261813</v>
+        <v>1.93809774087593</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.116547113291332</v>
+        <v>1.938097567905449</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.1165468157821051</v>
+        <v>1.938097270396222</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.1165468019444665</v>
+        <v>1.938097256558584</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.1165464352470473</v>
+        <v>1.938096889861164</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.1165464352470473</v>
+        <v>1.938096889861164</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.1165463729776742</v>
+        <v>1.938096827591791</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.1165462691953857</v>
+        <v>1.938096723809503</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.116546096224905</v>
+        <v>1.938096550839022</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.1165461446566396</v>
+        <v>1.938096599270756</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.1165457848780395</v>
+        <v>1.938096239492157</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.1165457433651241</v>
+        <v>1.938096197979241</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.1165457987156778</v>
+        <v>1.938096253329795</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.1165458540662318</v>
+        <v>1.938096308680349</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.1165458955791472</v>
+        <v>1.938096350193264</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.1165456257451971</v>
+        <v>1.938096080359314</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.116545681095751</v>
+        <v>1.938096135709868</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.1165458263909549</v>
+        <v>1.938096281005072</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.1165457917968587</v>
+        <v>1.938096246410976</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.1165457779592201</v>
+        <v>1.938096232573337</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.1165458679038703</v>
+        <v>1.938096322517987</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.1165461861695549</v>
+        <v>1.938096640783672</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.1165460062802548</v>
+        <v>1.938096460894372</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.1165460477931702</v>
+        <v>1.938096502407287</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.1165458609850509</v>
+        <v>1.938096315599168</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.1165459301732434</v>
+        <v>1.93809638478736</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.1165457295274856</v>
+        <v>1.938096184141603</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.116545771040401</v>
+        <v>1.938096225654518</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.1165457987156778</v>
+        <v>1.938096253329795</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_2_000006.xlsx
+++ b/out/Attention-S4_repeat_2_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>2.648249220197787</v>
+        <v>1.981656608135625</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.648249220197787</v>
+        <v>1.981656608135625</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>3.248249220197787</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>3.248249220197787</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>3.248249220197787</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>3.248249220197787</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3648012947504813</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>3.248249220197787</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>3.248249220197787</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>3.248249220197787</v>
+        <v>1.981656608135625</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>3.248249220197787</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>3.248249220197787</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>3.248249220197787</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.3299763727307028</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.3299763727307027</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.648249220197787</v>
+        <v>0.3299763727307027</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.3299763727307027</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3648012947504813</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.3299763727307027</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>3.248249220197787</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>3.248249220197787</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>3.248249220197787</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3648012947504813</v>
+        <v>0.5299763727307026</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3648012947504813</v>
+        <v>-0.2958637449717586</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.3299763727307026</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.648249220197787</v>
+        <v>1.155816490433164</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>3.248249220197787</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3648012947504813</v>
+        <v>0.5299763727307026</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3648012947504813</v>
+        <v>-0.2958637449717586</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>-4.308016012911685e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.05544752186925173</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>0.110999977121687</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>-0.01280511187186988</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>0.04259932983725274</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>0.04259932983725274</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC48" t="n">
-        <v>-1.869338789233006e-05</v>
+        <v>0.04253863795231481</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0574299681421693</v>
+        <v>0.1864585963220929</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.1149559245705088</v>
+        <v>0.4158271132423594</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01098863939975576</v>
+        <v>0.03567668935860802</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.07941910241671558</v>
+        <v>0.3004499201728478</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01924764405023872</v>
+        <v>0.06249132245732342</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.1069311376639663</v>
+        <v>0.3897732400350452</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.01053957933579559</v>
+        <v>0.03422252227408025</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.1087471929584714</v>
+        <v>0.3956730983817587</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.004350125898167171</v>
+        <v>0.0141342032802804</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.1068990254588795</v>
+        <v>0.3896835007947315</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.005420851300212872</v>
+        <v>0.01761000437162611</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.1133911867290754</v>
+        <v>0.4107722667200747</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.003262045427652021</v>
+        <v>0.01060196810272412</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.1144914816815832</v>
+        <v>0.4143559783201404</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.002477911654897917</v>
+        <v>0.008059971359505607</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.1161859408406725</v>
+        <v>0.4198691461577471</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.001093200817303421</v>
+        <v>0.003561371395121383</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.1158924719073689</v>
+        <v>0.4189278191844544</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.0008676852873857978</v>
+        <v>0.002824921654470708</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.5299763727307025</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.1165327356065775</v>
+        <v>0.4210161979375137</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.0004277560855517731</v>
+        <v>0.001398330427714131</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>3.248249220197787</v>
+        <v>0.5299763727307025</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.1165200119845022</v>
+        <v>0.4209861312158287</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0002451912641241405</v>
+        <v>0.000812485409521901</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3648012947504813</v>
+        <v>0.5299763727307025</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.1165853208673967</v>
+        <v>0.4212095275994253</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0001200956320620703</v>
+        <v>0.0004022881043881357</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3648012947504813</v>
+        <v>0.5299763727307025</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1165801651148903</v>
+        <v>0.4212040204982413</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.824225957239745e-05</v>
+        <v>0.0001962253713667192</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>3.248249220197787</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.1165735642006141</v>
+        <v>0.4211938920859943</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>3.17141805569301e-05</v>
+        <v>0.0001118178472265958</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>3.248249220197787</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.1165787170341371</v>
+        <v>0.4212216601171827</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>6.159850569859539e-06</v>
+        <v>3.517546205149434e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3648012947504813</v>
+        <v>0.5299763727307026</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.1165615258697967</v>
+        <v>0.4211767571654355</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.73737344181313e-06</v>
+        <v>1.521212032543939e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3648012947504813</v>
+        <v>-0.2958637449717586</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.1165566004203176</v>
+        <v>0.4211719808169978</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>-2.553803869891494e-06</v>
+        <v>4.784784520434025e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.1165521992917126</v>
+        <v>0.4211687743653045</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>-2.629819553036738e-06</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.1165470441031398</v>
+        <v>0.421163387881147</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.11654758377104</v>
+        <v>0.4211600032626961</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.1165472516677168</v>
+        <v>0.4211543358324223</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.1165476322027745</v>
+        <v>0.4211547163674801</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.1165478605238092</v>
+        <v>0.4211549446885148</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.1165479504684592</v>
+        <v>0.4211550346331648</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.5299763727307025</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.1165470925348743</v>
+        <v>0.4211541766995799</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>3.248249220197787</v>
+        <v>0.5299763727307025</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.116547320855909</v>
+        <v>0.4211544050206146</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3648012947504813</v>
+        <v>0.5299763727307025</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.1165465251916973</v>
+        <v>0.4211536093564029</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3648012947504813</v>
+        <v>0.5299763727307025</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.1165465874610704</v>
+        <v>0.421153671625776</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>3.248249220197787</v>
+        <v>0.5299763727307025</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.1165466151363472</v>
+        <v>0.4211536993010528</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3648012947504813</v>
+        <v>0.5299763727307025</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.1165467673503705</v>
+        <v>0.4211538515150761</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3648012947504813</v>
+        <v>-0.2958637449717586</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.1165464214094088</v>
+        <v>0.4211535055741144</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.1165464975164204</v>
+        <v>0.421153581681126</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.116546663568082</v>
+        <v>0.4211537477327876</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.1165470233466821</v>
+        <v>0.4211541075113877</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.1165470441031398</v>
+        <v>0.4211541282678454</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.1165471478854283</v>
+        <v>0.4211542320501339</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.116547376206463</v>
+        <v>0.4211544603711685</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.1165472516677168</v>
+        <v>0.4211543358324223</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.1165472793429936</v>
+        <v>0.4211543635076992</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.1165473346935476</v>
+        <v>0.4211544188582532</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.1165475976086783</v>
+        <v>0.4211546817733839</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.1165475145828475</v>
+        <v>0.4211545987475531</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.1165473070182707</v>
+        <v>0.4211543911829763</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.116547320855909</v>
+        <v>0.4211544050206146</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.1165474592322938</v>
+        <v>0.4211545433969994</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.1165471755607051</v>
+        <v>0.4211542597254107</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.1165470025902244</v>
+        <v>0.42115408675493</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.1165468988079359</v>
+        <v>0.4211539829726414</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.1165470441031398</v>
+        <v>0.4211541282678454</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.116547286261813</v>
+        <v>0.4211543704265186</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.116547113291332</v>
+        <v>0.4211541974560376</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.1165468157821051</v>
+        <v>0.4211538999468107</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.1165468019444665</v>
+        <v>0.4211538861091721</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.1165464352470473</v>
+        <v>0.4211535194117529</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.1165464352470473</v>
+        <v>0.4211535194117529</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.1165463729776742</v>
+        <v>0.4211534571423798</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.1165462691953857</v>
+        <v>0.4211533533600914</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.116546096224905</v>
+        <v>0.4211531803896106</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.1165461446566396</v>
+        <v>0.4211532288213451</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.1165457848780395</v>
+        <v>0.4211528690427451</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.1165457433651241</v>
+        <v>0.4211528275298297</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.1165457987156778</v>
+        <v>0.4211528828803834</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.1165458540662318</v>
+        <v>0.4211529382309374</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.1165458955791472</v>
+        <v>0.4211529797438527</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.1165456257451971</v>
+        <v>0.4211527099099027</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.116545681095751</v>
+        <v>0.4211527652604566</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.1165458263909549</v>
+        <v>0.4211529105556605</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.1165457917968587</v>
+        <v>0.4211528759615643</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.1165457779592201</v>
+        <v>0.4211528621239257</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.1165458679038703</v>
+        <v>0.4211529520685759</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.1165461861695549</v>
+        <v>0.4211532703342605</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.1165460062802548</v>
+        <v>0.4211530904449604</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.1165460477931702</v>
+        <v>0.4211531319578758</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.1165458609850509</v>
+        <v>0.4211529451497565</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.1165459301732434</v>
+        <v>0.421153014337949</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.1165457295274856</v>
+        <v>0.4211528136921912</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.116545771040401</v>
+        <v>0.4211528552051065</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.1165457987156778</v>
+        <v>0.4211528828803834</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_2_000006.xlsx
+++ b/out/Attention-S4_repeat_2_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.009781870990991592</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.981656608135625</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.006628703325986862</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.981656608135625</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.005201723426580429</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.181656608135626</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.003782838582992554</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.181656608135626</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.003324799239635468</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.181656608135626</v>
+        <v>-0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.0003472492098808289</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.355816490433164</v>
+        <v>-0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-8.166208863258362e-05</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.355816490433164</v>
+        <v>-0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.001182157546281815</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.355816490433164</v>
+        <v>-0.3</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.002695634961128235</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.181656608135626</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.00165993720293045</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.981656608135625</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.000901494175195694</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.181656608135626</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.0009509846568107605</v>
       </c>
       <c r="JB13" t="n">
-        <v>2.181656608135626</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.0005850978195667267</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.355816490433164</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.001190580427646637</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.3299763727307028</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.001542285084724426</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.002469126135110855</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.002543020993471146</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.0009560883045196533</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.3299763727307027</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.0008193664252758026</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.3299763727307027</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.0001849345862865448</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.3299763727307027</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.0007078684866428375</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.002593759447336197</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.001850977540016174</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.002034805715084076</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.001995470374822617</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.0009469091892242432</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.3299763727307027</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.0002084784209728241</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.355816490433164</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.0004586689174175262</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.181656608135626</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.0007373839616775513</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.355816490433164</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.001631196588277817</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.5299763727307026</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.002250093966722488</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.2958637449717586</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.0005899630486965179</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.0004241392016410828</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.16</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.0003536827862262726</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.3299763727307026</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.0009668804705142975</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.155816490433164</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.0005386359989643097</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.355816490433164</v>
+        <v>0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.001500669866800308</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.5299763727307026</v>
+        <v>0.16</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.002328690141439438</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.2958637449717586</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.001837689429521561</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.0006878040730953217</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.001618649810552597</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.001303620636463165</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.003016673028469086</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>-4.308016012911685e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.05544752186925173</v>
+        <v>0</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.006271559745073318</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.110999977121687</v>
+        <v>-2.473933803720865e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.01280511187186988</v>
+        <v>-0.03429838284158258</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.002015702426433563</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.04259932983725274</v>
+        <v>-0.03432312217961985</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.0006890185177326202</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.04259932983725274</v>
+        <v>-0.03432312217961985</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.001950755715370178</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.04253863795231481</v>
+        <v>-0.0344099241933648</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.1864585963220929</v>
+        <v>0.2666743965680925</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.004079796373844147</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.4158271132423594</v>
+        <v>0.4994702051801453</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.03567668935860802</v>
+        <v>0.05102514098856752</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.00517742708325386</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.3004499201728478</v>
+        <v>0.3344567308507269</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.06249132245732342</v>
+        <v>0.08937537356836209</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.006471931934356689</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.3897732400350452</v>
+        <v>0.4622076604774688</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.03422252227408025</v>
+        <v>0.04894520698911964</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.008625216782093048</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.3956730983817587</v>
+        <v>0.4706457062284609</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0141342032802804</v>
+        <v>0.02021528010096247</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.005351755768060684</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.3896835007947315</v>
+        <v>0.4620792725836088</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.01761000437162611</v>
+        <v>0.0251860138272594</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.007344894111156464</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.4107722667200747</v>
+        <v>0.4922403948376682</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01060196810272412</v>
+        <v>0.01516519755718781</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.009972978383302689</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.4143559783201404</v>
+        <v>0.4973679216661548</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.008059971359505607</v>
+        <v>0.0115292205676155</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.007840216159820557</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.4198691461577471</v>
+        <v>0.5052547990369357</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.003561371395121383</v>
+        <v>0.005096627530454386</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.0133962519466877</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.4189278191844544</v>
+        <v>0.5039106977437192</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.002824921654470708</v>
+        <v>0.00404314996027227</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.007146157324314117</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.5299763727307025</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.4210161979375137</v>
+        <v>0.5068989007414936</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001398330427714131</v>
+        <v>0.002001187171170648</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.003731824457645416</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.5299763727307025</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.4209861312158287</v>
+        <v>0.50685807452316</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.000812485409521901</v>
+        <v>0.001161589498997446</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.01170315966010094</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.5299763727307025</v>
+        <v>0.16</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4212095275994253</v>
+        <v>0.5071794149392678</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0004022881043881357</v>
+        <v>0.0005797493498715376</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.009493034332990646</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.5299763727307025</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.4212040204982413</v>
+        <v>0.5071736868868533</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0001962253713667192</v>
+        <v>0.0002824648162381703</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.002731505781412125</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.355816490433164</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4211938920859943</v>
+        <v>0.5071613754096846</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001118178472265958</v>
+        <v>0.0001618826388951368</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.008987214416265488</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.355816490433164</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4212216601171827</v>
+        <v>0.5072029882138586</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>3.517546205149434e-05</v>
+        <v>5.079925284929769e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.005455188453197479</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.5299763727307026</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4211767571654355</v>
+        <v>0.5071414604364659</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.521212032543939e-05</v>
+        <v>2.419528491452356e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.001251049339771271</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.2958637449717586</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4211719808169978</v>
+        <v>0.5071367834887225</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.784784520434025e-06</v>
+        <v>9.677176780651038e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.007748100906610489</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4211687743653045</v>
+        <v>0.5071343734883037</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>-2.596391060734771e-07</v>
+        <v>2.110541340889784e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.01352202892303467</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.421163387881147</v>
+        <v>0.5071288318155733</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-2.090799254370459e-06</v>
+        <v>8.184014912590811e-07</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.01130276173353195</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4211600032626961</v>
+        <v>0.5071259832428715</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.01462532952427864</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4211543358324223</v>
+        <v>0.5071203158125978</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.01667294651269913</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4211547163674801</v>
+        <v>0.5071206963476554</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.01616282388567924</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4211549446885148</v>
+        <v>0.5071209246686902</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.007841788232326508</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4211550346331648</v>
+        <v>0.5071210146133401</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.002372156828641891</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.5299763727307025</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4211541766995799</v>
+        <v>0.5071201566797553</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.0003960840404033661</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.5299763727307025</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4211544050206146</v>
+        <v>0.50712038500079</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.00287235900759697</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.5299763727307025</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4211536093564029</v>
+        <v>0.5071195893365783</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.001902975142002106</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.5299763727307025</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.421153671625776</v>
+        <v>0.5071196516059514</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.0004603154957294464</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.5299763727307025</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4211536993010528</v>
+        <v>0.5071196792812283</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.006009116768836975</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.5299763727307025</v>
+        <v>0.3</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4211538515150761</v>
+        <v>0.5071198314952515</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.01410998404026031</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.2958637449717586</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4211535055741144</v>
+        <v>0.5071194855542898</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.01658802479505539</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.421153581681126</v>
+        <v>0.5071195616613015</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.01405728980898857</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4211537477327876</v>
+        <v>0.507119727712963</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.01175430417060852</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4211541075113877</v>
+        <v>0.507120087491563</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.006329286843538284</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4211541282678454</v>
+        <v>0.5071201082480208</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.003643885254859924</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4211542320501339</v>
+        <v>0.5071202120303092</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.004435420036315918</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4211544603711685</v>
+        <v>0.507120440351344</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.006629332900047302</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4211543358324223</v>
+        <v>0.5071203158125978</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.00816870853304863</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4211543635076992</v>
+        <v>0.5071203434878746</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.006644923239946365</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4211544188582532</v>
+        <v>0.5071203988384285</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.01115494593977928</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4211546817733839</v>
+        <v>0.5071206617535593</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.01306213065981865</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4211545987475531</v>
+        <v>0.5071205787277284</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.01374796032905579</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4211543911829763</v>
+        <v>0.5071203711631517</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.01324455067515373</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4211544050206146</v>
+        <v>0.50712038500079</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.01676448062062263</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4211545433969994</v>
+        <v>0.5071205233771747</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.01650897040963173</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4211542597254107</v>
+        <v>0.5071202397055861</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.0129130631685257</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.42115408675493</v>
+        <v>0.5071200667351053</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.009976595640182495</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.3</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4211539829726414</v>
+        <v>0.5071199629528168</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.009062331169843674</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4211541282678454</v>
+        <v>0.5071201082480208</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.009015902876853943</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4211543704265186</v>
+        <v>0.507120350406694</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.008784398436546326</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4211541974560376</v>
+        <v>0.507120177436213</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.009264808148145676</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4211538999468107</v>
+        <v>0.507119879926986</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.01299963146448135</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4211538861091721</v>
+        <v>0.5071198660893476</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.0180695615708828</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4211535194117529</v>
+        <v>0.5071194993919284</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.01769625023007393</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4211535194117529</v>
+        <v>0.5071194993919284</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.01473287865519524</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4211534571423798</v>
+        <v>0.5071194371225552</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.01251614838838577</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4211533533600914</v>
+        <v>0.5071193333402667</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.0113377533853054</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4211531803896106</v>
+        <v>0.507119160369786</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.0104583241045475</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4211532288213451</v>
+        <v>0.5071192088015205</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.009176928550004959</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4211528690427451</v>
+        <v>0.5071188490229205</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.00913214311003685</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4211528275298297</v>
+        <v>0.507118807510005</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.00978880375623703</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4211528828803834</v>
+        <v>0.5071188628605587</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.01087624207139015</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4211529382309374</v>
+        <v>0.5071189182111128</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.01062380895018578</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.3</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4211529797438527</v>
+        <v>0.5071189597240281</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.01143128797411919</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4211527099099027</v>
+        <v>0.507118689890078</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.01111787930130959</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4211527652604566</v>
+        <v>0.5071187452406319</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.009842723608016968</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.16</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4211529105556605</v>
+        <v>0.5071188905358359</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.009571414440870285</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4211528759615643</v>
+        <v>0.5071188559417397</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.008621085435152054</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4211528621239257</v>
+        <v>0.5071188421041011</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.004618160426616669</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4211529520685759</v>
+        <v>0.5071189320487512</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.004159767180681229</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4211532703342605</v>
+        <v>0.5071192503144359</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.001920673996210098</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4211530904449604</v>
+        <v>0.5071190704251358</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.00084691122174263</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4211531319578758</v>
+        <v>0.5071191119380511</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.004725154489278793</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4211529451497565</v>
+        <v>0.5071189251299318</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.005913697183132172</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.421153014337949</v>
+        <v>0.5071189943181243</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.005591712892055511</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4211528136921912</v>
+        <v>0.5071187936723666</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.005941294133663177</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.3000000000000002</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4211528552051065</v>
+        <v>0.5071188351852819</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.003499023616313934</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.4400000000000002</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4211528828803834</v>
+        <v>0.5071188628605587</v>
       </c>
     </row>
   </sheetData>
